--- a/feedback_forms/014_digital_banking_experience_report_form--feedback_forms.xlsx
+++ b/feedback_forms/014_digital_banking_experience_report_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>account_details</t>
+          <t>What type of account do you have with the bank?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>issue_description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>Can you describe any issues you experienced with your account?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>issue_description</t>
+          <t>feedback_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>issue_description</t>
+          <t>Do you think the bank's service was helpful?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>feedback_type</t>
+          <t>feedback_rating</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feedback_type</t>
+          <t>How would you rate the bank's service?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback_rating</t>
+          <t>bank_contact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feedback_rating</t>
+          <t>What is your bank's contact information?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bank_contact</t>
+          <t>bank_phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bank_contact</t>
+          <t>Bank Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bank_phone</t>
+          <t>bank_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bank_phone</t>
+          <t>Bank Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bank_email</t>
+          <t>bank_website</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bank_email</t>
+          <t>Bank Website</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bank_website</t>
+          <t>bank_social_media</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bank_website</t>
+          <t>Is the bank active on social media?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bank_app</t>
+          <t>account_number</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bank_app</t>
+          <t>What is your account number?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bank_social_media</t>
+          <t>account_type</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bank_social_media</t>
+          <t>Account Type</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>account_manager</t>
+          <t>bank_app</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>account_manager</t>
+          <t>How do you like the bank's mobile app?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>account_number</t>
+          <t>account_manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>account_number</t>
+          <t>Who is your account manager's name?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feedback_message</t>
+          <t>Do you have any additional feedback for the bank?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>account_number_type</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>What type of account number do you have?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>account_number_type</t>
+          <t>bank_social_media_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>Bank Social Media 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bank_app</t>
+          <t>account_details_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bank_app</t>
+          <t>Please provide any additional details about your account.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bank_social_media</t>
+          <t>issue_description_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bank_social_media</t>
+          <t>Can you provide more details about any issues you experienced with your account?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>account_manager</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>account_manager</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>account_number</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>account_number</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>feedback_message</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>feedback_message</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>account_type</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>account_type</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>account_number_type</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>account_number_type</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>account_details</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>account_details</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>bank_app</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>bank_app</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1188,6 +1027,40 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>feedback_rating_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>feedback_rating_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>very_poor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
